--- a/data/trans_bre/P05A_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P05A_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,4</t>
+          <t>6,8</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>37,51%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 10,08</t>
+          <t>-1,28; 9,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 7,41</t>
+          <t>-5,44; 7,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 4,68</t>
+          <t>-8,06; 5,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 16,99</t>
+          <t>-2,69; 14,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 38,59</t>
+          <t>-3,87; 37,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,33; 23,0</t>
+          <t>-14,29; 21,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-21,22; 14,73</t>
+          <t>-20,88; 17,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 133,71</t>
+          <t>-12,9; 106,16</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,17</t>
+          <t>1,85</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 8,97</t>
+          <t>-0,88; 9,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 3,79</t>
+          <t>-6,59; 4,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 7,96</t>
+          <t>-3,95; 7,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 7,0</t>
+          <t>-4,1; 8,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 35,81</t>
+          <t>-2,9; 36,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-16,63; 10,18</t>
+          <t>-15,47; 11,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 24,46</t>
+          <t>-10,05; 23,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-41,01; 49,77</t>
+          <t>-18,87; 54,97</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-3,02</t>
+          <t>-0,47</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-14,28%</t>
+          <t>-2,24%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,21; 12,81</t>
+          <t>2,39; 13,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 7,48</t>
+          <t>-3,06; 7,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 9,28</t>
+          <t>-1,08; 8,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 1,58</t>
+          <t>-5,2; 4,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,59; 47,23</t>
+          <t>6,97; 47,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 21,3</t>
+          <t>-7,55; 21,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 30,54</t>
+          <t>-2,85; 28,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-37,59; 7,99</t>
+          <t>-20,71; 22,59</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,62</t>
+          <t>0,6</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 8,59</t>
+          <t>-2,89; 8,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 9,66</t>
+          <t>-2,46; 9,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 5,79</t>
+          <t>-5,65; 5,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 14,94</t>
+          <t>-3,4; 4,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 29,2</t>
+          <t>-8,34; 28,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 26,31</t>
+          <t>-5,98; 25,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,3; 16,13</t>
+          <t>-13,26; 16,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-13,84; 178,63</t>
+          <t>-14,91; 25,19</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,49</t>
+          <t>5,01</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>30,99%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 12,86</t>
+          <t>-0,83; 13,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 3,15</t>
+          <t>-11,31; 2,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 6,57</t>
+          <t>-6,41; 6,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 8,15</t>
+          <t>0,86; 8,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 48,43</t>
+          <t>-2,7; 49,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-23,05; 8,77</t>
+          <t>-24,44; 6,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-16,21; 19,34</t>
+          <t>-15,81; 19,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 57,56</t>
+          <t>3,53; 62,06</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27,43</t>
+          <t>0,22</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>156,26%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 13,05</t>
+          <t>-0,89; 13,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 4,21</t>
+          <t>-11,7; 4,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 5,67</t>
+          <t>-9,45; 5,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 57,9</t>
+          <t>-3,96; 4,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 56,11</t>
+          <t>-2,55; 56,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-24,05; 10,15</t>
+          <t>-23,96; 10,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-22,45; 16,57</t>
+          <t>-21,38; 16,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 399,13</t>
+          <t>-19,11; 29,66</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>1,46</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 9,03</t>
+          <t>-7,03; 8,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 9,73</t>
+          <t>-6,27; 9,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 7,86</t>
+          <t>-6,74; 7,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 4,91</t>
+          <t>-2,61; 5,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-22,6; 36,81</t>
+          <t>-20,87; 38,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,85; 30,73</t>
+          <t>-14,75; 29,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-21,27; 30,55</t>
+          <t>-20,92; 28,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-19,97; 41,47</t>
+          <t>-16,15; 46,1</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6,39</t>
+          <t>1,83</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,53; 7,11</t>
+          <t>2,5; 6,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 2,67</t>
+          <t>-2,15; 2,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 2,93</t>
+          <t>-1,76; 2,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,94; 21,95</t>
+          <t>-0,28; 3,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,4; 25,16</t>
+          <t>8,29; 24,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 7,02</t>
+          <t>-5,26; 6,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 8,31</t>
+          <t>-4,78; 8,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,79; 129,75</t>
+          <t>-1,47; 20,26</t>
         </is>
       </c>
     </row>
